--- a/ET-release8.1/Unity/Assets/Config/Excel/AvatarConfig@c.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/AvatarConfig@c.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>#</t>
   </si>
@@ -71,7 +71,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Armor_1_Body</t>
+    <t>Armor_Body</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor/Armor_Armor_1_Left.prefab</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor_Left</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -444,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:G6"/>
+  <dimension ref="C2:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -517,7 +525,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -528,6 +536,53 @@
       <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
